--- a/玉米大豆历史数据/玉米基差/North Dakota Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/North Dakota Basis.xlsx
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O440"/>
+  <dimension ref="A1:O441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9467,6 +9467,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B441" t="n">
+        <v>-85</v>
+      </c>
+      <c r="C441" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9478,7 +9489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O440"/>
+  <dimension ref="A1:O441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18345,6 +18356,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B441" t="n">
+        <v>-72.5</v>
+      </c>
+      <c r="C441" t="n">
+        <v>-5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18356,7 +18378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O440"/>
+  <dimension ref="A1:O441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27223,6 +27245,17 @@
         <v>-2.5</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B441" t="n">
+        <v>-82.5</v>
+      </c>
+      <c r="C441" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27234,7 +27267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O438"/>
+  <dimension ref="A1:O439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -36061,6 +36094,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B439" t="n">
+        <v>-100</v>
+      </c>
+      <c r="C439" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36072,7 +36116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O440"/>
+  <dimension ref="A1:O441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -44939,6 +44983,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B441" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C441" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/North Dakota Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/North Dakota Basis.xlsx
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O441"/>
+  <dimension ref="A1:O442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9478,6 +9478,17 @@
         <v>-2.5</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B442" t="n">
+        <v>-85</v>
+      </c>
+      <c r="C442" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9489,7 +9500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O441"/>
+  <dimension ref="A1:O442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18367,6 +18378,17 @@
         <v>-5</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B442" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C442" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18378,7 +18400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O441"/>
+  <dimension ref="A1:O442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27256,6 +27278,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B442" t="n">
+        <v>-82.5</v>
+      </c>
+      <c r="C442" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27267,7 +27300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O439"/>
+  <dimension ref="A1:O440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -36105,6 +36138,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B440" t="n">
+        <v>-100</v>
+      </c>
+      <c r="C440" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36116,7 +36160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O441"/>
+  <dimension ref="A1:O442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -44994,6 +45038,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B442" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C442" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/North Dakota Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/North Dakota Basis.xlsx
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O442"/>
+  <dimension ref="A1:O443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9489,6 +9489,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B443" t="n">
+        <v>-85</v>
+      </c>
+      <c r="C443" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9500,7 +9511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O442"/>
+  <dimension ref="A1:O443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18389,6 +18400,17 @@
         <v>-2.5</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B443" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C443" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18400,7 +18422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O442"/>
+  <dimension ref="A1:O443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27289,6 +27311,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B443" t="n">
+        <v>-82.5</v>
+      </c>
+      <c r="C443" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27300,7 +27333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O440"/>
+  <dimension ref="A1:O441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -36149,6 +36182,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B441" t="n">
+        <v>-100</v>
+      </c>
+      <c r="C441" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36160,7 +36204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O442"/>
+  <dimension ref="A1:O443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -45049,6 +45093,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B443" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C443" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/North Dakota Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/North Dakota Basis.xlsx
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O443"/>
+  <dimension ref="A1:O444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9500,6 +9500,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="5" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B444" t="n">
+        <v>-85</v>
+      </c>
+      <c r="C444" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9511,7 +9522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O443"/>
+  <dimension ref="A1:O444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18411,6 +18422,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="5" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B444" t="n">
+        <v>-77.5</v>
+      </c>
+      <c r="C444" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18422,7 +18444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O443"/>
+  <dimension ref="A1:O444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27322,6 +27344,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="5" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B444" t="n">
+        <v>-82.5</v>
+      </c>
+      <c r="C444" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27333,7 +27366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O441"/>
+  <dimension ref="A1:O442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -36193,6 +36226,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="5" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B442" t="n">
+        <v>-100</v>
+      </c>
+      <c r="C442" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36204,7 +36248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O443"/>
+  <dimension ref="A1:O444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -45104,6 +45148,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="5" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B444" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C444" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/North Dakota Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/North Dakota Basis.xlsx
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O444"/>
+  <dimension ref="A1:O445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9511,6 +9511,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B445" t="n">
+        <v>-85</v>
+      </c>
+      <c r="C445" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9522,7 +9533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O444"/>
+  <dimension ref="A1:O445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18433,6 +18444,17 @@
         <v>-2.5</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B445" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C445" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18444,7 +18466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O444"/>
+  <dimension ref="A1:O445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27355,6 +27377,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B445" t="n">
+        <v>-87.5</v>
+      </c>
+      <c r="C445" t="n">
+        <v>-5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27366,7 +27399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O442"/>
+  <dimension ref="A1:O443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -36237,6 +36270,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B443" t="n">
+        <v>-100</v>
+      </c>
+      <c r="C443" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36248,7 +36292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O444"/>
+  <dimension ref="A1:O445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -45159,6 +45203,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B445" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C445" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/North Dakota Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/North Dakota Basis.xlsx
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O447"/>
+  <dimension ref="A1:O448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9544,6 +9544,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B448" t="n">
+        <v>-85</v>
+      </c>
+      <c r="C448" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9555,7 +9566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O447"/>
+  <dimension ref="A1:O448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18499,6 +18510,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B448" t="n">
+        <v>-82.5</v>
+      </c>
+      <c r="C448" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18510,7 +18532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O447"/>
+  <dimension ref="A1:O448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27454,6 +27476,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B448" t="n">
+        <v>-87.5</v>
+      </c>
+      <c r="C448" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27465,7 +27498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O445"/>
+  <dimension ref="A1:O446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -36369,6 +36402,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="446">
+      <c r="A446" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B446" t="n">
+        <v>-100</v>
+      </c>
+      <c r="C446" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36380,7 +36424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O447"/>
+  <dimension ref="A1:O448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -45324,6 +45368,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B448" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C448" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/North Dakota Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/North Dakota Basis.xlsx
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O448"/>
+  <dimension ref="A1:O449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9555,6 +9555,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="449">
+      <c r="A449" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B449" t="n">
+        <v>-85</v>
+      </c>
+      <c r="C449" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9566,7 +9577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O448"/>
+  <dimension ref="A1:O449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18521,6 +18532,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="449">
+      <c r="A449" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B449" t="n">
+        <v>-82.5</v>
+      </c>
+      <c r="C449" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18532,7 +18554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O448"/>
+  <dimension ref="A1:O449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27487,6 +27509,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="449">
+      <c r="A449" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B449" t="n">
+        <v>-87.5</v>
+      </c>
+      <c r="C449" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27498,7 +27531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O446"/>
+  <dimension ref="A1:O447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -36413,6 +36446,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="447">
+      <c r="A447" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B447" t="n">
+        <v>-100</v>
+      </c>
+      <c r="C447" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36424,7 +36468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O448"/>
+  <dimension ref="A1:O449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -45379,6 +45423,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="449">
+      <c r="A449" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B449" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C449" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
